--- a/data/out/gateB_pilot.xlsx
+++ b/data/out/gateB_pilot.xlsx
@@ -1097,7 +1097,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E7" s="14" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1128,7 +1132,7 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
@@ -1163,7 +1167,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E8" s="14" t="n"/>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Mont Blanc</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1194,7 +1202,7 @@
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R8" s="12" t="inlineStr">
@@ -1229,8 +1237,16 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Gobi</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>No Length</t>
@@ -1254,7 +1270,11 @@
       <c r="K9" s="13" t="n">
         <v>1018</v>
       </c>
-      <c r="L9" s="14" t="n"/>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
+        </is>
+      </c>
       <c r="R9" s="12" t="inlineStr">
         <is>
           <t>US</t>
@@ -1287,7 +1307,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E10" s="14" t="n"/>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Deauville</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1318,7 +1342,7 @@
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R10" s="12" t="inlineStr">
@@ -1353,7 +1377,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E11" s="14" t="n"/>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1384,7 +1412,7 @@
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R11" s="12" t="inlineStr">
@@ -1419,7 +1447,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E12" s="14" t="n"/>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1450,7 +1482,7 @@
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R12" s="12" t="inlineStr">
@@ -1485,7 +1517,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1516,7 +1552,7 @@
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R13" s="12" t="inlineStr">
@@ -1551,7 +1587,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E14" s="14" t="n"/>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Stromboli</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1582,7 +1622,7 @@
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R14" s="12" t="inlineStr">
@@ -1617,7 +1657,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E15" s="14" t="n"/>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1648,7 +1692,7 @@
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
@@ -1683,7 +1727,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E16" s="14" t="n"/>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1714,7 +1762,7 @@
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R16" s="12" t="inlineStr">
@@ -1749,7 +1797,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E17" s="14" t="n"/>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Syracuse</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1780,7 +1832,7 @@
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R17" s="12" t="inlineStr">
@@ -1815,7 +1867,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E18" s="14" t="n"/>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Tahoe</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1846,7 +1902,7 @@
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
@@ -1881,7 +1937,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E19" s="14" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Macao</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1912,7 +1972,7 @@
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
@@ -1947,7 +2007,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E20" s="14" t="n"/>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -1978,7 +2042,7 @@
       </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
@@ -2013,7 +2077,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E21" s="14" t="n"/>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2044,7 +2112,7 @@
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="R21" s="12" t="inlineStr">
@@ -2079,7 +2147,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E22" s="14" t="n"/>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Mont Blanc</t>
+        </is>
+      </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2145,7 +2217,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E23" s="14" t="n"/>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Gobi</t>
+        </is>
+      </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2211,7 +2287,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E24" s="14" t="n"/>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Deauville</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2277,7 +2357,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E25" s="14" t="n"/>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2343,7 +2427,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E26" s="14" t="n"/>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2409,7 +2497,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E27" s="14" t="n"/>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2475,7 +2567,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E28" s="14" t="n"/>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2541,7 +2637,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E29" s="14" t="n"/>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2607,7 +2707,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E30" s="14" t="n"/>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Stromboli</t>
+        </is>
+      </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2673,7 +2777,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E31" s="14" t="n"/>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2739,7 +2847,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E32" s="14" t="n"/>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2805,7 +2917,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E33" s="14" t="n"/>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Tahoe</t>
+        </is>
+      </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2871,7 +2987,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E34" s="14" t="n"/>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Huahine</t>
+        </is>
+      </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -2937,7 +3057,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E35" s="14" t="n"/>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Macao</t>
+        </is>
+      </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -3003,7 +3127,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E36" s="14" t="n"/>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -3069,7 +3197,11 @@
           <t>NARS</t>
         </is>
       </c>
-      <c r="E37" s="14" t="n"/>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
           <t>30 ml</t>
@@ -5578,7 +5710,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>"ID":"0194251070360" … "color":"None"</t>
+          <t>"ID":"0194251070360" … "color":"Oslo"</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5620,9 +5752,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5630,6 +5767,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070360&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -5637,12 +5779,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>"ID":"0194251070360" … "color":"None"</t>
+          <t>"ID":"0194251070360" … "color":"Oslo"</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5826,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>"ID":"0194251070360" … "color":"None"</t>
+          <t>"ID":"0194251070360" … "color":"Oslo"</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5753,7 +5895,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>"ID":"0194251070360" … "color":"None"</t>
+          <t>"ID":"0194251070360" … "color":"Oslo"</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5802,7 +5944,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5822,7 +5964,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6052,7 +6194,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>"ID":"0194251070384" … "color":"None"</t>
+          <t>"ID":"0194251070384" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6094,9 +6236,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mont Blanc</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6104,6 +6251,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070384&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -6111,12 +6263,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>"ID":"0194251070384" … "color":"None"</t>
+          <t>"ID":"0194251070384" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6310,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>"ID":"0194251070384" … "color":"None"</t>
+          <t>"ID":"0194251070384" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6227,7 +6379,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>"ID":"0194251070384" … "color":"None"</t>
+          <t>"ID":"0194251070384" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6276,7 +6428,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6296,7 +6448,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6568,14 +6720,19 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gobi</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.narscosmetics.eu/en/light-reflecting-advanced-skincare-foundation/0194251070421.html</t>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6585,12 +6742,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>"ID":"0194251070421" (PDP product-state self-anchor)</t>
+          <t>"barcode":"194251070421" … shade 'Gobi'</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>brand site had no value; GTIN-anchored retailer is the single source</t>
         </is>
       </c>
     </row>
@@ -6605,14 +6762,34 @@
           <t>size</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>dom</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>"barcode":"194251070421" … shade 'Gobi'</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>size not found</t>
+          <t>brand site had no value; GTIN-anchored retailer is the single source</t>
         </is>
       </c>
     </row>
@@ -6723,9 +6900,14 @@
           <t>ingredients</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6740,12 +6922,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>"ID":"0194251070421" (PDP product-state self-anchor)</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>no INGREDIENTS accordion on brand PDP</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
@@ -6970,7 +7152,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>"ID":"0194251070469" … "color":"None"</t>
+          <t>"ID":"0194251070469" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7012,9 +7194,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Deauville</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7022,6 +7209,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070469&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -7029,12 +7221,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>"ID":"0194251070469" … "color":"None"</t>
+          <t>"ID":"0194251070469" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7268,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>"ID":"0194251070469" … "color":"None"</t>
+          <t>"ID":"0194251070469" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7145,7 +7337,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>"ID":"0194251070469" … "color":"None"</t>
+          <t>"ID":"0194251070469" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7194,7 +7386,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7214,7 +7406,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7444,7 +7636,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>"ID":"0194251070506" … "color":"None"</t>
+          <t>"ID":"0194251070506" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7486,9 +7678,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7496,6 +7693,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070506&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -7503,12 +7705,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>"ID":"0194251070506" … "color":"None"</t>
+          <t>"ID":"0194251070506" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7752,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>"ID":"0194251070506" … "color":"None"</t>
+          <t>"ID":"0194251070506" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7619,7 +7821,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>"ID":"0194251070506" … "color":"None"</t>
+          <t>"ID":"0194251070506" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7668,7 +7870,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7688,7 +7890,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7918,7 +8120,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>"ID":"0194251070520" … "color":"None"</t>
+          <t>"ID":"0194251070520" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7960,9 +8162,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7970,6 +8177,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070520&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -7977,12 +8189,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>"ID":"0194251070520" … "color":"None"</t>
+          <t>"ID":"0194251070520" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8236,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>"ID":"0194251070520" … "color":"None"</t>
+          <t>"ID":"0194251070520" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8093,7 +8305,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>"ID":"0194251070520" … "color":"None"</t>
+          <t>"ID":"0194251070520" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8142,7 +8354,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8162,7 +8374,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8392,7 +8604,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>"ID":"0194251070544" … "color":"None"</t>
+          <t>"ID":"0194251070544" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8434,9 +8646,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8444,6 +8661,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070544&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -8451,12 +8673,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>"ID":"0194251070544" … "color":"None"</t>
+          <t>"ID":"0194251070544" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8720,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>"ID":"0194251070544" … "color":"None"</t>
+          <t>"ID":"0194251070544" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -8567,7 +8789,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>"ID":"0194251070544" … "color":"None"</t>
+          <t>"ID":"0194251070544" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8616,7 +8838,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8636,7 +8858,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8866,7 +9088,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>"ID":"0194251070629" … "color":"None"</t>
+          <t>"ID":"0194251070629" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8908,9 +9130,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Stromboli</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8918,6 +9145,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070629&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -8925,12 +9157,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>"ID":"0194251070629" … "color":"None"</t>
+          <t>"ID":"0194251070629" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -8972,7 +9204,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>"ID":"0194251070629" … "color":"None"</t>
+          <t>"ID":"0194251070629" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9041,7 +9273,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>"ID":"0194251070629" … "color":"None"</t>
+          <t>"ID":"0194251070629" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9090,7 +9322,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9110,7 +9342,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -9340,7 +9572,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>"ID":"0194251070667" … "color":"None"</t>
+          <t>"ID":"0194251070667" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9382,9 +9614,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9392,6 +9629,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070667&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -9399,12 +9641,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>"ID":"0194251070667" … "color":"None"</t>
+          <t>"ID":"0194251070667" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9688,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>"ID":"0194251070667" … "color":"None"</t>
+          <t>"ID":"0194251070667" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9515,7 +9757,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>"ID":"0194251070667" … "color":"None"</t>
+          <t>"ID":"0194251070667" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9564,7 +9806,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9584,7 +9826,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9814,7 +10056,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>"ID":"0194251070681" … "color":"None"</t>
+          <t>"ID":"0194251070681" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9856,9 +10098,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9866,6 +10113,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070681&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -9873,12 +10125,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>"ID":"0194251070681" … "color":"None"</t>
+          <t>"ID":"0194251070681" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -9920,7 +10172,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>"ID":"0194251070681" … "color":"None"</t>
+          <t>"ID":"0194251070681" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9989,7 +10241,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>"ID":"0194251070681" … "color":"None"</t>
+          <t>"ID":"0194251070681" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10038,7 +10290,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10058,7 +10310,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10288,7 +10540,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>"ID":"0194251070728" … "color":"None"</t>
+          <t>"ID":"0194251070728" … "color":"Syracuse"</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10330,9 +10582,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Syracuse</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -10340,6 +10597,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070728&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -10347,12 +10609,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>"ID":"0194251070728" … "color":"None"</t>
+          <t>"ID":"0194251070728" … "color":"Syracuse"</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10656,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>"ID":"0194251070728" … "color":"None"</t>
+          <t>"ID":"0194251070728" … "color":"Syracuse"</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10463,7 +10725,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>"ID":"0194251070728" … "color":"None"</t>
+          <t>"ID":"0194251070728" … "color":"Syracuse"</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10512,7 +10774,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10532,7 +10794,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10762,7 +11024,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>"ID":"0194251070742" … "color":"None"</t>
+          <t>"ID":"0194251070742" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -10804,9 +11066,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tahoe</t>
+        </is>
+      </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10814,6 +11081,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070742&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -10821,12 +11093,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>"ID":"0194251070742" … "color":"None"</t>
+          <t>"ID":"0194251070742" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -10868,7 +11140,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>"ID":"0194251070742" … "color":"None"</t>
+          <t>"ID":"0194251070742" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -10937,7 +11209,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>"ID":"0194251070742" … "color":"None"</t>
+          <t>"ID":"0194251070742" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -10986,7 +11258,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11006,7 +11278,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11236,7 +11508,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>"ID":"0194251070865" … "color":"None"</t>
+          <t>"ID":"0194251070865" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11278,9 +11550,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Macao</t>
+        </is>
+      </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11288,6 +11565,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070865&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -11295,12 +11577,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>"ID":"0194251070865" … "color":"None"</t>
+          <t>"ID":"0194251070865" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11624,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>"ID":"0194251070865" … "color":"None"</t>
+          <t>"ID":"0194251070865" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -11411,7 +11693,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>"ID":"0194251070865" … "color":"None"</t>
+          <t>"ID":"0194251070865" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -11460,7 +11742,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11480,7 +11762,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -11710,7 +11992,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>"ID":"0194251070926" … "color":"None"</t>
+          <t>"ID":"0194251070926" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -11752,9 +12034,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11762,6 +12049,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=4251070926&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -11769,12 +12061,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>"ID":"0194251070926" … "color":"None"</t>
+          <t>"ID":"0194251070926" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -11816,7 +12108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>"ID":"0194251070926" … "color":"None"</t>
+          <t>"ID":"0194251070926" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -11885,7 +12177,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>"ID":"0194251070926" … "color":"None"</t>
+          <t>"ID":"0194251070926" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -11934,7 +12226,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -11954,7 +12246,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -12184,7 +12476,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>"ID":"0194251150130" … "color":"None"</t>
+          <t>"ID":"0194251150130" … "color":"Lima"</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -12226,9 +12518,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -12236,6 +12533,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000141&amp;dwvar_999NAC0000141_color=194251150130&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-light-reflecting-foundation-30ml-various-shades/13496963/</t>
+        </is>
+      </c>
       <c r="G270" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -12243,12 +12545,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>"ID":"0194251150130" … "color":"None"</t>
+          <t>"ID":"0194251150130" … "color":"Lima"</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12592,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>"ID":"0194251150130" … "color":"None"</t>
+          <t>"ID":"0194251150130" … "color":"Lima"</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -12359,7 +12661,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>"ID":"0194251150130" … "color":"None"</t>
+          <t>"ID":"0194251150130" … "color":"Lima"</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -12408,7 +12710,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -12428,7 +12730,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEP</t>
+          <t xml:space="preserve">WATER/AQUA/EAU · C9-12 ALKANE · BUTYLENE GLYCOL · UNDECANE · TRIDECANE · ISODECYL NEOPENTANOATE · HYDROGENATED POLYISOBUTENE · POLYGLYCERYL-6 POLYRICINOLEATE · </t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -12658,7 +12960,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>"ID":"0607845066019" … "color":"None"</t>
+          <t>"ID":"0607845066019" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -12700,9 +13002,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Mont Blanc</t>
+        </is>
+      </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -12710,6 +13017,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066019&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G284" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -12717,12 +13029,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>"ID":"0607845066019" … "color":"None"</t>
+          <t>"ID":"0607845066019" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -12764,7 +13076,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>"ID":"0607845066019" … "color":"None"</t>
+          <t>"ID":"0607845066019" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -12833,7 +13145,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>"ID":"0607845066019" … "color":"None"</t>
+          <t>"ID":"0607845066019" … "color":"Mont Blanc"</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13132,7 +13444,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>"ID":"0607845066033" … "color":"None"</t>
+          <t>"ID":"0607845066033" … "color":"Gobi"</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13174,9 +13486,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Gobi</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -13184,6 +13501,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066033&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G298" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -13191,12 +13513,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>"ID":"0607845066033" … "color":"None"</t>
+          <t>"ID":"0607845066033" … "color":"Gobi"</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13560,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>"ID":"0607845066033" … "color":"None"</t>
+          <t>"ID":"0607845066033" … "color":"Gobi"</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13307,7 +13629,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>"ID":"0607845066033" … "color":"None"</t>
+          <t>"ID":"0607845066033" … "color":"Gobi"</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13606,7 +13928,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>"ID":"0607845066057" … "color":"None"</t>
+          <t>"ID":"0607845066057" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -13648,9 +13970,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Deauville</t>
+        </is>
+      </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -13658,6 +13985,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066057&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G312" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -13665,12 +13997,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>"ID":"0607845066057" … "color":"None"</t>
+          <t>"ID":"0607845066057" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -13712,7 +14044,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>"ID":"0607845066057" … "color":"None"</t>
+          <t>"ID":"0607845066057" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -13781,7 +14113,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>"ID":"0607845066057" … "color":"None"</t>
+          <t>"ID":"0607845066057" … "color":"Deauville"</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14080,7 +14412,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>"ID":"0607845066064" … "color":"None"</t>
+          <t>"ID":"0607845066064" … "color":"Vienna"</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -14122,9 +14454,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -14132,6 +14469,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066064&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G326" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -14139,12 +14481,12 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>"ID":"0607845066064" … "color":"None"</t>
+          <t>"ID":"0607845066064" … "color":"Vienna"</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14528,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>"ID":"0607845066064" … "color":"None"</t>
+          <t>"ID":"0607845066064" … "color":"Vienna"</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -14255,7 +14597,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>"ID":"0607845066064" … "color":"None"</t>
+          <t>"ID":"0607845066064" … "color":"Vienna"</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -14554,7 +14896,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>"ID":"0607845066071" … "color":"None"</t>
+          <t>"ID":"0607845066071" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -14596,9 +14938,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -14606,6 +14953,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066071&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G340" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -14613,12 +14965,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>"ID":"0607845066071" … "color":"None"</t>
+          <t>"ID":"0607845066071" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -14660,7 +15012,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>"ID":"0607845066071" … "color":"None"</t>
+          <t>"ID":"0607845066071" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -14729,7 +15081,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>"ID":"0607845066071" … "color":"None"</t>
+          <t>"ID":"0607845066071" … "color":"Fiji"</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -15028,7 +15380,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>"ID":"0607845066088" … "color":"None"</t>
+          <t>"ID":"0607845066088" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -15070,9 +15422,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -15080,6 +15437,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066088&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G354" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -15087,12 +15449,12 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>"ID":"0607845066088" … "color":"None"</t>
+          <t>"ID":"0607845066088" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15496,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>"ID":"0607845066088" … "color":"None"</t>
+          <t>"ID":"0607845066088" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -15203,7 +15565,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>"ID":"0607845066088" … "color":"None"</t>
+          <t>"ID":"0607845066088" … "color":"Punjab"</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -15502,7 +15864,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>"ID":"0607845066095" … "color":"None"</t>
+          <t>"ID":"0607845066095" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -15544,9 +15906,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -15554,6 +15921,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066095&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G368" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -15561,12 +15933,12 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>"ID":"0607845066095" … "color":"None"</t>
+          <t>"ID":"0607845066095" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15980,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>"ID":"0607845066095" … "color":"None"</t>
+          <t>"ID":"0607845066095" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -15677,7 +16049,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>"ID":"0607845066095" … "color":"None"</t>
+          <t>"ID":"0607845066095" … "color":"Patagonia"</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -15976,7 +16348,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>"ID":"0607845066118" … "color":"None"</t>
+          <t>"ID":"0607845066118" … "color":"Santa Fe"</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -16018,9 +16390,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -16028,6 +16405,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066118&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G382" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -16035,12 +16417,12 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>"ID":"0607845066118" … "color":"None"</t>
+          <t>"ID":"0607845066118" … "color":"Santa Fe"</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16464,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>"ID":"0607845066118" … "color":"None"</t>
+          <t>"ID":"0607845066118" … "color":"Santa Fe"</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -16151,7 +16533,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>"ID":"0607845066118" … "color":"None"</t>
+          <t>"ID":"0607845066118" … "color":"Santa Fe"</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -16450,7 +16832,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>"ID":"0607845066132" … "color":"None"</t>
+          <t>"ID":"0607845066132" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -16492,9 +16874,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Stromboli</t>
+        </is>
+      </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -16502,6 +16889,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066132&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G396" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -16509,12 +16901,12 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>"ID":"0607845066132" … "color":"None"</t>
+          <t>"ID":"0607845066132" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16948,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>"ID":"0607845066132" … "color":"None"</t>
+          <t>"ID":"0607845066132" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -16625,7 +17017,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>"ID":"0607845066132" … "color":"None"</t>
+          <t>"ID":"0607845066132" … "color":"Stromboli"</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -16924,7 +17316,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>"ID":"0607845066156" … "color":"None"</t>
+          <t>"ID":"0607845066156" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -16966,9 +17358,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -16976,6 +17373,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066156&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G410" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -16983,12 +17385,12 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>"ID":"0607845066156" … "color":"None"</t>
+          <t>"ID":"0607845066156" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -17030,7 +17432,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>"ID":"0607845066156" … "color":"None"</t>
+          <t>"ID":"0607845066156" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -17099,7 +17501,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>"ID":"0607845066156" … "color":"None"</t>
+          <t>"ID":"0607845066156" … "color":"Barcelona"</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -17398,7 +17800,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>"ID":"0607845066163" … "color":"None"</t>
+          <t>"ID":"0607845066163" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -17440,9 +17842,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -17450,6 +17857,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066163&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G424" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -17457,12 +17869,12 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>"ID":"0607845066163" … "color":"None"</t>
+          <t>"ID":"0607845066163" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -17504,7 +17916,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>"ID":"0607845066163" … "color":"None"</t>
+          <t>"ID":"0607845066163" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -17573,7 +17985,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>"ID":"0607845066163" … "color":"None"</t>
+          <t>"ID":"0607845066163" … "color":"Valencia"</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -17872,7 +18284,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>"ID":"0607845066194" … "color":"None"</t>
+          <t>"ID":"0607845066194" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -17914,9 +18326,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Tahoe</t>
+        </is>
+      </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -17924,6 +18341,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066194&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G438" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -17931,12 +18353,12 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>"ID":"0607845066194" … "color":"None"</t>
+          <t>"ID":"0607845066194" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -17978,7 +18400,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>"ID":"0607845066194" … "color":"None"</t>
+          <t>"ID":"0607845066194" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -18047,7 +18469,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>"ID":"0607845066194" … "color":"None"</t>
+          <t>"ID":"0607845066194" … "color":"Tahoe"</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -18346,7 +18768,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>"ID":"0607845066217" … "color":"None"</t>
+          <t>"ID":"0607845066217" … "color":"Huahine"</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -18388,9 +18810,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Huahine</t>
+        </is>
+      </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -18398,6 +18825,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066217&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G452" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -18405,12 +18837,12 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>"ID":"0607845066217" … "color":"None"</t>
+          <t>"ID":"0607845066217" … "color":"Huahine"</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18884,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>"ID":"0607845066217" … "color":"None"</t>
+          <t>"ID":"0607845066217" … "color":"Huahine"</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -18521,7 +18953,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>"ID":"0607845066217" … "color":"None"</t>
+          <t>"ID":"0607845066217" … "color":"Huahine"</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -18820,7 +19252,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>"ID":"0607845066255" … "color":"None"</t>
+          <t>"ID":"0607845066255" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -18862,9 +19294,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Macao</t>
+        </is>
+      </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -18872,6 +19309,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066255&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G466" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -18879,12 +19321,12 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>"ID":"0607845066255" … "color":"None"</t>
+          <t>"ID":"0607845066255" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -18926,7 +19368,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>"ID":"0607845066255" … "color":"None"</t>
+          <t>"ID":"0607845066255" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -18995,7 +19437,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>"ID":"0607845066255" … "color":"None"</t>
+          <t>"ID":"0607845066255" … "color":"Macao"</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -19294,7 +19736,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>"ID":"0607845066286" … "color":"None"</t>
+          <t>"ID":"0607845066286" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -19336,9 +19778,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -19346,6 +19793,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066286&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G480" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -19353,12 +19805,12 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>"ID":"0607845066286" … "color":"None"</t>
+          <t>"ID":"0607845066286" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -19400,7 +19852,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>"ID":"0607845066286" … "color":"None"</t>
+          <t>"ID":"0607845066286" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -19469,7 +19921,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>"ID":"0607845066286" … "color":"None"</t>
+          <t>"ID":"0607845066286" … "color":"New Caledonia"</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -19768,7 +20220,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>"ID":"0607845066309" … "color":"None"</t>
+          <t>"ID":"0607845066309" … "color":"Namibia"</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -19810,9 +20262,14 @@
           <t>color_name</t>
         </is>
       </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -19820,6 +20277,11 @@
           <t>https://www.narscosmetics.eu/on/demandware.store/Sites-nars_eu-Site/default/Product-Variation?pid=999NAC0000065&amp;dwvar_999NAC0000065_color=7845066309&amp;Quantity=1&amp;format=ajax</t>
         </is>
       </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>https://www.lookfantastic.com/p/nars-natural-radiant-longwear-foundation-various-shades/11640948/</t>
+        </is>
+      </c>
       <c r="G494" t="inlineStr">
         <is>
           <t>sfcc_api</t>
@@ -19827,12 +20289,12 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>"ID":"0607845066309" … "color":"None"</t>
+          <t>"ID":"0607845066309" … "color":"Namibia"</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>two independent families agree</t>
         </is>
       </c>
     </row>
@@ -19874,7 +20336,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>"ID":"0607845066309" … "color":"None"</t>
+          <t>"ID":"0607845066309" … "color":"Namibia"</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -19943,7 +20405,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>"ID":"0607845066309" … "color":"None"</t>
+          <t>"ID":"0607845066309" … "color":"Namibia"</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -20215,7 +20677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E286"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20226,7 +20688,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-02T20:44:00+00:00</t>
+          <t>2026-07-02T20:52:27+00:00</t>
         </is>
       </c>
     </row>
@@ -20423,7 +20885,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -20443,7 +20905,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -20453,7 +20915,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24">
@@ -20530,7 +20992,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -20540,14 +21002,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>194251070360</t>
+          <t>194251070384</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -20569,12 +21031,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>194251070384</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -20584,14 +21046,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>194251070384</t>
+          <t>194251070469</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -20613,12 +21075,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070506</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -20628,14 +21090,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070520</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -20657,12 +21119,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070544</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -20672,19 +21134,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>no INGREDIENTS accordion on brand PDP</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070629</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -20694,19 +21156,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>size not found</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>194251070469</t>
+          <t>194251070667</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -20716,14 +21178,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>194251070469</t>
+          <t>194251070681</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -20745,12 +21207,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>194251070506</t>
+          <t>194251070728</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -20760,14 +21222,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>194251070506</t>
+          <t>194251070742</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -20789,12 +21251,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>194251070520</t>
+          <t>194251070865</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -20804,14 +21266,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>194251070520</t>
+          <t>194251070926</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -20833,12 +21295,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>194251070544</t>
+          <t>194251143040</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -20848,14 +21310,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>no color-code rule matched — fail closed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>194251070544</t>
+          <t>194251143040</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -20877,12 +21339,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>194251070629</t>
+          <t>194251143057</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -20892,14 +21354,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>no color-code rule matched — fail closed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>194251070629</t>
+          <t>194251143057</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20921,12 +21383,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>194251070667</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -20936,14 +21398,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>no color-code rule matched — fail closed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>194251070667</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -20965,12 +21427,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>194251070681</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -20980,14 +21442,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>194251070681</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -21009,12 +21471,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>194251070728</t>
+          <t>194251150130</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -21024,14 +21486,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>194251070728</t>
+          <t>607845066019</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -21053,12 +21515,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>194251070742</t>
+          <t>607845066033</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -21068,14 +21530,14 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>194251070742</t>
+          <t>607845066057</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -21097,12 +21559,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>194251070865</t>
+          <t>607845066064</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -21112,14 +21574,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>194251070865</t>
+          <t>607845066071</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -21141,12 +21603,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>194251070926</t>
+          <t>607845066088</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -21156,14 +21618,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>194251070926</t>
+          <t>607845066095</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -21185,12 +21647,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>194251143040</t>
+          <t>607845066118</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -21200,14 +21662,14 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>no color-code rule matched — fail closed</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>194251143040</t>
+          <t>607845066132</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -21229,12 +21691,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>194251143057</t>
+          <t>607845066156</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -21244,14 +21706,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>no color-code rule matched — fail closed</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>194251143057</t>
+          <t>607845066163</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -21273,12 +21735,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066194</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -21288,14 +21750,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>no color-code rule matched — fail closed</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066217</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -21317,7 +21779,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066255</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -21339,7 +21801,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066286</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -21361,12 +21823,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>194251150130</t>
+          <t>607845066309</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>expiry_on_pack</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -21376,745 +21838,880 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>requires product knowledge (Phase 1)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>194251150130</t>
+          <t>194251070360</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>607845066019</t>
+          <t>194251070360</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>607845066019</t>
+          <t>194251070360</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>607845066033</t>
+          <t>194251070360</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>607845066033</t>
+          <t>194251070360</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>607845066057</t>
+          <t>194251070384</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>607845066057</t>
+          <t>194251070384</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>607845066064</t>
+          <t>194251070384</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>607845066064</t>
+          <t>194251070384</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>607845066071</t>
+          <t>194251070384</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>607845066071</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>607845066088</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>607845066088</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>color_name</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Gobi</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>brand site had no value; GTIN-anchored retailer is the single source</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>607845066095</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>607845066095</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>607845066118</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>size</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>30 ml</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>brand site had no value; GTIN-anchored retailer is the single source</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>607845066118</t>
+          <t>194251070421</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>607845066132</t>
+          <t>194251070469</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>607845066132</t>
+          <t>194251070469</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>607845066156</t>
+          <t>194251070469</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>607845066156</t>
+          <t>194251070469</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>607845066163</t>
+          <t>194251070469</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>607845066163</t>
+          <t>194251070506</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>607845066194</t>
+          <t>194251070506</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>607845066194</t>
+          <t>194251070506</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>607845066217</t>
+          <t>194251070506</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>607845066217</t>
+          <t>194251070506</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>607845066255</t>
+          <t>194251070520</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>607845066255</t>
+          <t>194251070520</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>607845066286</t>
+          <t>194251070520</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>607845066286</t>
+          <t>194251070520</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>607845066309</t>
+          <t>194251070520</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>no shade on brand site — no-color convention pending (open question 3)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>607845066309</t>
+          <t>194251070544</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>expiry_on_pack</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>requires product knowledge (Phase 1)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>194251070360</t>
+          <t>194251070544</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -22124,24 +22721,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>194251070360</t>
+          <t>194251070544</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -22151,24 +22748,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>194251070360</t>
+          <t>194251070544</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -22178,73 +22775,73 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>194251070360</t>
+          <t>194251070544</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>194251070360</t>
+          <t>194251070629</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>194251070384</t>
+          <t>194251070629</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -22254,24 +22851,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>194251070384</t>
+          <t>194251070629</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -22281,24 +22878,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>194251070384</t>
+          <t>194251070629</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -22308,73 +22905,73 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>194251070384</t>
+          <t>194251070629</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>194251070384</t>
+          <t>194251070667</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070667</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -22384,24 +22981,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070667</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -22411,24 +23008,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070667</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -22438,19 +23035,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>194251070421</t>
+          <t>194251070667</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -22472,7 +23069,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>194251070469</t>
+          <t>194251070681</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -22499,7 +23096,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>194251070469</t>
+          <t>194251070681</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -22526,7 +23123,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>194251070469</t>
+          <t>194251070681</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -22553,7 +23150,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>194251070469</t>
+          <t>194251070681</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -22568,7 +23165,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -22580,7 +23177,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>194251070469</t>
+          <t>194251070681</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -22602,7 +23199,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>194251070506</t>
+          <t>194251070728</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -22629,7 +23226,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>194251070506</t>
+          <t>194251070728</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -22656,7 +23253,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>194251070506</t>
+          <t>194251070728</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -22683,7 +23280,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>194251070506</t>
+          <t>194251070728</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -22698,7 +23295,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -22710,7 +23307,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>194251070506</t>
+          <t>194251070728</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -22732,7 +23329,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>194251070520</t>
+          <t>194251070742</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -22759,7 +23356,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>194251070520</t>
+          <t>194251070742</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -22786,7 +23383,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>194251070520</t>
+          <t>194251070742</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -22813,7 +23410,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>194251070520</t>
+          <t>194251070742</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -22828,7 +23425,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -22840,7 +23437,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>194251070520</t>
+          <t>194251070742</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -22862,7 +23459,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>194251070544</t>
+          <t>194251070865</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -22889,7 +23486,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>194251070544</t>
+          <t>194251070865</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -22916,7 +23513,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>194251070544</t>
+          <t>194251070865</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -22943,7 +23540,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>194251070544</t>
+          <t>194251070865</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -22958,7 +23555,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -22970,7 +23567,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>194251070544</t>
+          <t>194251070865</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -22992,7 +23589,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>194251070629</t>
+          <t>194251070926</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -23019,7 +23616,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>194251070629</t>
+          <t>194251070926</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -23046,7 +23643,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>194251070629</t>
+          <t>194251070926</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -23073,7 +23670,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>194251070629</t>
+          <t>194251070926</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -23088,7 +23685,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -23100,7 +23697,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>194251070629</t>
+          <t>194251070926</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -23122,7 +23719,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>194251070667</t>
+          <t>194251143040</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -23137,24 +23734,24 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>Makeup</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>rule makeup:eyeshadow on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>194251070667</t>
+          <t>194251143040</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -23164,24 +23761,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>default for non-DG category 'Makeup'</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>194251070667</t>
+          <t>194251143040</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -23191,73 +23788,73 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>194251070667</t>
+          <t>194251143040</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>194251070667</t>
+          <t>194251143057</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Makeup</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>rule makeup:eyeshadow on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>194251070681</t>
+          <t>194251143057</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -23267,24 +23864,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>default for non-DG category 'Makeup'</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>194251070681</t>
+          <t>194251143057</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -23294,51 +23891,46 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>194251070681</t>
+          <t>194251143057</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>194251070681</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -23348,46 +23940,51 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>Makeup</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>rule makeup:eyeshadow on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>194251070681</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>color_name</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Ablaze</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>194251070728</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -23397,24 +23994,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>default for non-DG category 'Makeup'</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>194251070728</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -23424,24 +24021,24 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>194251070728</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>size</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -23451,24 +24048,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1.6 g</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>194251070728</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>style_name</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -23478,19 +24075,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>Total Seduction Eyeshadow Stick</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>194251070728</t>
+          <t>194251146997</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -23512,7 +24109,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>194251070742</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -23527,19 +24124,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>Makeup</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>rule makeup:eyeshadow on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>194251070742</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -23554,24 +24151,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>rule lexicon:orgasm</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>194251070742</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>color_name</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -23581,24 +24178,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Orgasm</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>194251070742</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -23608,46 +24205,51 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>default for non-DG category 'Makeup'</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>194251070742</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>194251070865</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>size</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -23657,24 +24259,24 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>1.6 g</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>194251070865</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>style_name</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -23684,51 +24286,46 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>Total Seduction Eyeshadow Stick</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>194251070865</t>
+          <t>194251147000</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>194251070865</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -23738,46 +24335,51 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>Makeup</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>rule makeup:eyeshadow on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>194251070865</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1010</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>rule lexicon:laguna</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>194251070926</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>color_name</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -23787,24 +24389,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>Laguna</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>194251070926</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -23814,24 +24416,24 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
+          <t>default for non-DG category 'Makeup'</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>194251070926</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -23841,24 +24443,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Foundation'</t>
+          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>194251070926</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>size</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -23868,73 +24470,73 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>1.6 g</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>194251070926</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>style_name</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Total Seduction Eyeshadow Stick</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>single source family (brand site); validator had no data</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>194251143040</t>
+          <t>194251147024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Makeup</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>rule makeup:eyeshadow on site name; enum-validated</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>194251143040</t>
+          <t>194251150130</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -23944,24 +24546,24 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Makeup'</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>194251143040</t>
+          <t>194251150130</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -23971,46 +24573,51 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>194251143040</t>
+          <t>194251150130</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>194251143057</t>
+          <t>194251150130</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -24020,51 +24627,46 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Makeup</t>
+          <t>WATER/AQUA/EAU, C9-12 ALKANE, BUTYLENE GLYCOL, UNDECANE, TRIDECANE, ISODECYL NEOPENTANOATE, HYDROGENATED POLYISOBUTENE, POLYGLYCERYL-6 POLYRICINOLEATE, POLYGLYCERYL-2 DIISOSTEARATE, DISTEARDIMONIUM HECTORITE, DIISOSTEARYL MALATE, GLYCERIN, SYNTHETIC WAX, SODIUM CHLORIDE, OPHIOPOGON JAPONICUS ROOT EXTRACT, ASCOPHYLLUM NODOSUM EXTRACT, THEOBROMA CACAO (COCOA) SEED EXTRACT, CURCUMA LONGA (TURMERIC) ROOT EXTRACT, SILYBUM MARIANUM FRUIT EXTRACT, ALUMINUM HYDROXIDE, MAGNESIUM CHLORIDE, SODIUM DILAURAMIDOGLUTAMIDE LYSINE, TOCOPHEROL, COCO-CAPRYLATE/CAPRATE, ETHYLHEXYLGLYCERIN, PENTYLENE GLYCOL, HYDROXYPHENYL PROPAMIDOBENZOIC ACID, ASCORBYL PALMITATE, CITRIC ACID, SEA WATER/MARIS AQUA/EAU DE MER, TRISODIUM EDTA, BARIUM SULFATE, ALUMINA, CHLORPHENESIN, PHENOXYETHANOL, POTASSIUM SORBATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), MICA, TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>rule makeup:eyeshadow on site name; enum-validated</t>
+          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>194251143057</t>
+          <t>194251150130</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Makeup'</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>194251143057</t>
+          <t>607845066019</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -24074,46 +24676,51 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>194251143057</t>
+          <t>607845066019</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066019</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -24123,24 +24730,24 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Makeup</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>rule makeup:eyeshadow on site name; enum-validated</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066019</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -24150,51 +24757,46 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ablaze</t>
+          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066019</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Makeup'</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066033</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -24204,24 +24806,24 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066033</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -24231,24 +24833,24 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1.6 g</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066033</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>style_name</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -24258,73 +24860,73 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Total Seduction Eyeshadow Stick</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>194251146997</t>
+          <t>607845066033</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066033</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Makeup</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>rule makeup:eyeshadow on site name; enum-validated</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066057</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -24334,24 +24936,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>rule lexicon:orgasm</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066057</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -24361,19 +24963,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Orgasm</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066057</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -24393,14 +24995,14 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Makeup'</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066057</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -24415,51 +25017,46 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
+          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
+          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066057</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>1.6 g</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066064</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>style_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -24469,46 +25066,51 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Total Seduction Eyeshadow Stick</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>194251147000</t>
+          <t>607845066064</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>style_number</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>SINGLE_SOURCE</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>1018</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066064</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -24518,24 +25120,24 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Makeup</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>rule makeup:eyeshadow on site name; enum-validated</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066064</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>color_code</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -24545,51 +25147,46 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>rule lexicon:laguna</t>
+          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066064</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>color_name</t>
+          <t>style_number</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Laguna</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066071</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -24599,24 +25196,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>default for non-DG category 'Makeup'</t>
+          <t>rule foundation_family:foundation on site name; enum-validated</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066071</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ingredients</t>
+          <t>color_code</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -24626,24 +25223,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DIMETHICONE, TRIMETHYLSILOXYSILICATE, MICA, LAUROYL LYSINE, SILICA, POLYETHYLENE, SYNTHETIC WAX, STEAROXYMETHICONE/DIMETHICONE COPOLYMER, CAPRYLYL METHICONE, DICALCIUM PHOSPHATE, COPERNICIA CERIFERA (CARNAUBA) WAX/CERA CARNAUBA/CIRE DE CARNAUBA, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, POLYSILICONE-11, DISTEARDIMONIUM HECTORITE, PROPYLENE CARBONATE, POLYHYDROXYSTEARIC ACID, [+/-(MAY CONTAIN/PEUT CONTENIR): BLUE 1 LAKE (CI 42090), IRON OXIDES (CI 77491, CI 77492, CI 77499), MANGANESE VIOLET (CI 77742), TITANIUM DIOXIDE (CI 77891)]</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251143040 selected; one list per product (may-contain covers all shades)</t>
+          <t>rule foundation_family — pending confirmation (open question 2)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066071</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -24653,24 +25250,24 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1.6 g</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>default for non-DG category 'Foundation'</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066071</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>style_name</t>
+          <t>ingredients</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -24680,19 +25277,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Total Seduction Eyeshadow Stick</t>
+          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>single source family (brand site); validator had no data</t>
+          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>194251147024</t>
+          <t>607845066071</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -24714,7 +25311,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>194251150130</t>
+          <t>607845066088</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -24741,7 +25338,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>194251150130</t>
+          <t>607845066088</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -24768,7 +25365,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>194251150130</t>
+          <t>607845066088</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -24795,7 +25392,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>194251150130</t>
+          <t>607845066088</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -24810,19 +25407,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>BIOMIMETIC OAT: Helps soothe the skin and even out the complexion. JAPANESE LILYTURF: Helps restore the integrity of the barrier function of the skin. CACAO PEPTIDES : &amp; MILK THISTLE: Helps reduce the negative effects of blue light</t>
+          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>brand INCI captured with shade 0194251070360 selected; one list per product (may-contain covers all shades)</t>
+          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>194251150130</t>
+          <t>607845066088</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -24844,7 +25441,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>607845066019</t>
+          <t>607845066095</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -24871,7 +25468,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>607845066019</t>
+          <t>607845066095</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -24898,7 +25495,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>607845066019</t>
+          <t>607845066095</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -24925,7 +25522,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>607845066019</t>
+          <t>607845066095</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -24952,7 +25549,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>607845066019</t>
+          <t>607845066095</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -24974,7 +25571,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>607845066033</t>
+          <t>607845066118</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -25001,7 +25598,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>607845066033</t>
+          <t>607845066118</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -25028,7 +25625,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>607845066033</t>
+          <t>607845066118</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -25055,7 +25652,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>607845066033</t>
+          <t>607845066118</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -25082,7 +25679,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>607845066033</t>
+          <t>607845066118</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -25104,7 +25701,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>607845066057</t>
+          <t>607845066132</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -25131,7 +25728,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>607845066057</t>
+          <t>607845066132</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -25158,7 +25755,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>607845066057</t>
+          <t>607845066132</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -25185,7 +25782,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>607845066057</t>
+          <t>607845066132</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -25212,7 +25809,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>607845066057</t>
+          <t>607845066132</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -25234,7 +25831,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>607845066064</t>
+          <t>607845066156</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -25261,7 +25858,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>607845066064</t>
+          <t>607845066156</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -25288,7 +25885,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>607845066064</t>
+          <t>607845066156</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -25315,7 +25912,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>607845066064</t>
+          <t>607845066156</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -25342,7 +25939,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>607845066064</t>
+          <t>607845066156</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -25364,7 +25961,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>607845066071</t>
+          <t>607845066163</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -25391,7 +25988,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>607845066071</t>
+          <t>607845066163</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -25418,7 +26015,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>607845066071</t>
+          <t>607845066163</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -25445,7 +26042,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>607845066071</t>
+          <t>607845066163</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -25472,7 +26069,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>607845066071</t>
+          <t>607845066163</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -25494,7 +26091,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>607845066088</t>
+          <t>607845066194</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -25521,7 +26118,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>607845066088</t>
+          <t>607845066194</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -25548,7 +26145,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>607845066088</t>
+          <t>607845066194</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -25575,7 +26172,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>607845066088</t>
+          <t>607845066194</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -25602,7 +26199,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>607845066088</t>
+          <t>607845066194</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -25624,7 +26221,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>607845066095</t>
+          <t>607845066217</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -25651,7 +26248,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>607845066095</t>
+          <t>607845066217</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -25678,7 +26275,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>607845066095</t>
+          <t>607845066217</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -25705,7 +26302,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>607845066095</t>
+          <t>607845066217</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -25732,7 +26329,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>607845066095</t>
+          <t>607845066217</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -25754,7 +26351,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>607845066118</t>
+          <t>607845066255</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -25781,7 +26378,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>607845066118</t>
+          <t>607845066255</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -25808,7 +26405,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>607845066118</t>
+          <t>607845066255</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -25835,7 +26432,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>607845066118</t>
+          <t>607845066255</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -25862,7 +26459,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>607845066118</t>
+          <t>607845066255</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -25884,7 +26481,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>607845066132</t>
+          <t>607845066286</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -25911,7 +26508,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>607845066132</t>
+          <t>607845066286</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -25938,7 +26535,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>607845066132</t>
+          <t>607845066286</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -25965,7 +26562,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>607845066132</t>
+          <t>607845066286</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -25992,7 +26589,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>607845066132</t>
+          <t>607845066286</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -26014,7 +26611,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>607845066156</t>
+          <t>607845066309</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -26041,7 +26638,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>607845066156</t>
+          <t>607845066309</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -26068,7 +26665,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>607845066156</t>
+          <t>607845066309</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -26095,7 +26692,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>607845066156</t>
+          <t>607845066309</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -26122,7 +26719,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>607845066156</t>
+          <t>607845066309</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -26136,786 +26733,6 @@
         </is>
       </c>
       <c r="E256" t="inlineStr">
-        <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>607845066163</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>607845066163</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>color_code</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>607845066163</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>flammable</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>default for non-DG category 'Foundation'</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>607845066163</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>ingredients</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>607845066163</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>style_number</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>607845066194</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>607845066194</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>color_code</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>607845066194</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>flammable</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>default for non-DG category 'Foundation'</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>607845066194</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>ingredients</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>607845066194</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>style_number</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>607845066217</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>607845066217</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>color_code</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>607845066217</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>flammable</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>default for non-DG category 'Foundation'</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>607845066217</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>ingredients</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>607845066217</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>style_number</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>607845066255</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>607845066255</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>color_code</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>607845066255</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>flammable</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>default for non-DG category 'Foundation'</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>607845066255</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>ingredients</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>607845066255</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>style_number</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>607845066286</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>607845066286</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>color_code</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>607845066286</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>flammable</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>default for non-DG category 'Foundation'</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>607845066286</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>ingredients</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>607845066286</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>style_number</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>607845066309</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>rule foundation_family:foundation on site name; enum-validated</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>607845066309</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>color_code</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>rule foundation_family — pending confirmation (open question 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>607845066309</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>flammable</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>default for non-DG category 'Foundation'</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>607845066309</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>ingredients</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>DIMETHICONE, WATER/AQUA/EAU, PHENYL TRIMETHICONE, GLYCERIN, POLYMETHYLSILSESQUIOXANE, BORON NITRIDE, PEG-10 DIMETHICONE, DIMETHICONE CROSSPOLYMER, TRIMETHYLSILOXYSILICATE, PPG-3 BENZYL ETHER MYRISTATE, BIS-BUTYLDIMETHICONE POLYGLYCERYL-3, BUTYLENE GLYCOL, SORBITAN SESQUIISOSTEARATE, CITRULLUS LANATUS (WATERMELON) FRUIT EXTRACT, LENS ESCULENTA (LENTIL) FRUIT EXTRACT, PYRUS MALUS (APPLE) FRUIT EXTRACT, RUBUS IDAEUS (RASPBERRY) FRUIT EXTRACT, ALUMINUM DIMYRISTATE, TRIETHOXYCAPRYLYLSILANE, DISODIUM STEAROYL GLUTAMATE, HYDROGENATED POLYDECENE, TOCOPHEROL, STEARYL ALCOHOL, BEHENYL ALCOHOL, STEARIC ACID, BEHENIC ACID, PENTAERYTHRITYL TETRAETHYLHEXANOATE, PEG/PPG-14/7 DIMETHYL ETHER, SODIUM STEAROYL GLUTAMATE, POTASSIUM HYDROXIDE, SODIUM LACTATE, SODIUM PCA, DISTEARDIMONIUM HECTORITE, PENTAERYTHRITYL TETRA-DI-T-BUTYL HYDROXYHYDROCINNAMATE, MICA, BARIUM SULFATE, ALUMINA, TIN OXIDE, POLYSILICONE-2, PHENOXYETHANOL, POTASSIUM SORBATE, SODIUM BENZOATE, [+/-(MAY CONTAIN/PEUT CONTENIR): IRON OXIDES (CI 77491, CI 77492, CI 77499), TITANIUM DIOXIDE (CI 77891)]</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>brand INCI captured with shade 0607845066019 selected; one list per product (may-contain covers all shades); INCIDecoder weak support DISAGREES on base list [extra: water/​aqua/​eau, cyclopentasiloxane, peg/​ppg-14/​7 dimethyl ether, titanium dioxide (ci 77891, iron oxides (ci 77491)•iron oxides (ci 77492)•iron oxides (ci 77499, titanium dioxide (ci 77891] (https://incidecoder.com/products/nars-natural-radiant-longwear-foundation) — weak source, note only</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>607845066309</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>style_number</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
         <is>
           <t>NARS style-number prefix unconfirmed (open question 1) — fill manually</t>
         </is>
